--- a/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
+++ b/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTL\HTL 5\Diplomarbeit_Sicherung_Privat\Diplomarbeit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTL\HTL 5\Diplomarbeit_Sicherung_Privat\Diplomarbeit\3_Einkaufslisten_Komponenntenlisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A0C76B-90DC-4C41-A10A-878B855B61B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E00C5E-62D0-46D6-B0B0-46B65AB80A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12180" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>Hauptkomponenten</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>H (700-800) * B (400 - 600) * T (300)</t>
+  </si>
+  <si>
+    <t>Länge (Gewächshaus - Verteilerkasten)</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -388,7 +391,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -672,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.7265625" customWidth="1"/>
@@ -690,7 +692,7 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="13"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
@@ -702,7 +704,7 @@
       <c r="C2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E2" s="4"/>
@@ -1072,6 +1074,11 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D45" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1091,26 +1098,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1A147C5C4574A4CBD22C218932CFCEC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73e3fc346e235f1563653d0b735adab0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="934afb93-0c6a-4215-9c5f-1e6c0d084b74" xmlns:ns3="9772f75b-76b5-4c2b-8293-c04a292a8f98" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4bbf41fdf3feaa1d3e474fb90ecb8332" ns2:_="" ns3:_="">
     <xsd:import namespace="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
@@ -1317,26 +1304,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
-    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE955B8-3D42-4FAD-A4B0-6AF905D6A50D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1353,4 +1341,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
+    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
+++ b/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTL\HTL 5\Diplomarbeit_Sicherung_Privat\Diplomarbeit\3_Einkaufslisten_Komponenntenlisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E00C5E-62D0-46D6-B0B0-46B65AB80A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36784A0-3A71-4371-BF2C-1C62ACCB270B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12180" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
   <si>
     <t>Hauptkomponenten</t>
   </si>
@@ -176,12 +176,6 @@
     <t>Hauptenergiequelle</t>
   </si>
   <si>
-    <t>Display/Steuerung Option 1</t>
-  </si>
-  <si>
-    <t>Display Option 1a</t>
-  </si>
-  <si>
     <t>Victron Cerbo GX</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>Display 800x480, IP54, 2m Kabel</t>
   </si>
   <si>
-    <t>Versorgung</t>
-  </si>
-  <si>
     <t>12V AGM Super Cycle Batterie – 100Ah (M6)</t>
   </si>
   <si>
@@ -210,9 +201,6 @@
   </si>
   <si>
     <t>Christian Baumann</t>
-  </si>
-  <si>
-    <t>nur ausgeliehen</t>
   </si>
   <si>
     <t>bestellt</t>
@@ -373,7 +361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -391,6 +379,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -705,7 +694,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
@@ -731,27 +720,27 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
         <v>40</v>
@@ -768,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>42</v>
@@ -776,16 +765,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>42</v>
@@ -802,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>42</v>
@@ -810,7 +799,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -819,16 +808,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -982,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1002,83 +991,66 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" t="s">
         <v>48</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
         <v>50</v>
-      </c>
-      <c r="D33" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" t="s">
-        <v>52</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" t="s">
         <v>49</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" t="s">
         <v>51</v>
-      </c>
-      <c r="D34" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
         <v>72</v>
       </c>
-      <c r="D39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D43" t="s">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D44" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1098,6 +1070,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1A147C5C4574A4CBD22C218932CFCEC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73e3fc346e235f1563653d0b735adab0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="934afb93-0c6a-4215-9c5f-1e6c0d084b74" xmlns:ns3="9772f75b-76b5-4c2b-8293-c04a292a8f98" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4bbf41fdf3feaa1d3e474fb90ecb8332" ns2:_="" ns3:_="">
     <xsd:import namespace="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
@@ -1304,27 +1296,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
+    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE955B8-3D42-4FAD-A4B0-6AF905D6A50D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1341,23 +1332,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
-    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
+++ b/Diplomarbeit/3_Einkaufslisten_Komponenntenlisten/Komponentenliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTL\HTL 5\Diplomarbeit_Sicherung_Privat\Diplomarbeit\3_Einkaufslisten_Komponenntenlisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36784A0-3A71-4371-BF2C-1C62ACCB270B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D8AE54-DE4C-4072-9C9C-3AD7861880B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>Hauptkomponenten</t>
   </si>
@@ -50,15 +50,9 @@
     <t>Ladecontroller + Wechselrichter (230V) + PV/Netz-Umschaltung</t>
   </si>
   <si>
-    <t>Blade Sicherung 30A</t>
-  </si>
-  <si>
     <t>Haupt-Absicherung Akku (1x + Reserve)</t>
   </si>
   <si>
-    <t>Inline Blade Sicherungshalter</t>
-  </si>
-  <si>
     <t>Halter für 30A Blade-Sicherung</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>Kabelbinder</t>
   </si>
   <si>
-    <t>ESP32 DevKit C V4</t>
-  </si>
-  <si>
     <t>2 Paar</t>
   </si>
   <si>
@@ -110,9 +101,6 @@
     <t>Energie-Management-System</t>
   </si>
   <si>
-    <t>Zentrale Steuerung, Lastmanagement, IoT</t>
-  </si>
-  <si>
     <t>Stäubli MC4 Original 6 Paar</t>
   </si>
   <si>
@@ -200,15 +188,9 @@
     <t xml:space="preserve">Energiespeicher </t>
   </si>
   <si>
-    <t>Christian Baumann</t>
-  </si>
-  <si>
     <t>bestellt</t>
   </si>
   <si>
-    <t>amazon.de/-/en/dp/B0CZP1Q6DD?ref=ppx_yo2ov_dt_b_fed_asin_title</t>
-  </si>
-  <si>
     <t>127*76,5*3,5 cm</t>
   </si>
   <si>
@@ -242,25 +224,13 @@
     <t>220 * 171 * 330 mm</t>
   </si>
   <si>
-    <t>Verteilerschrank</t>
-  </si>
-  <si>
     <t>isolierter 12V→12V Converter für Sensorsystem (bis 18A)</t>
   </si>
   <si>
-    <t>H Multiplus + Batterie ca. 600mm + Kabelfürhung und Sicherungen (ca. 150-200mm) = ca. 700-800mm</t>
-  </si>
-  <si>
-    <t>B Batterie 330mm + ca. 70 für Kabelführung + vielleicht Multiplus neben Batterie (214mm) = 400-600mm</t>
-  </si>
-  <si>
-    <t>T Batterie 171mm + Kabelführung (ca. 70) = 241 gibt’s eher nicht daher ca. 300</t>
-  </si>
-  <si>
-    <t>H (700-800) * B (400 - 600) * T (300)</t>
-  </si>
-  <si>
-    <t>Länge (Gewächshaus - Verteilerkasten)</t>
+    <t>Sicherung 30A</t>
+  </si>
+  <si>
+    <t>Sicherungshalter</t>
   </si>
 </sst>
 </file>
@@ -361,7 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -379,7 +349,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -663,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.7265625" customWidth="1"/>
@@ -675,78 +644,78 @@
     <col min="7" max="7" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
@@ -757,194 +726,191 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
         <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
         <v>9</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
       <c r="F16" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -957,107 +923,65 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>16</v>
+      <c r="A24" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="10" t="s">
+      <c r="A25" s="12"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="12"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D43" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D44" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D45" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A25" r:id="rId1" xr:uid="{734513EE-8BD0-493B-9B76-0A58AFDD11A3}"/>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{734513EE-8BD0-493B-9B76-0A58AFDD11A3}"/>
     <hyperlink ref="A4" r:id="rId2" display="enjoysolar 150W Solar Panel" xr:uid="{69987FE7-C984-44CE-B012-F272C2F9439E}"/>
-    <hyperlink ref="A11" r:id="rId3" xr:uid="{6D31BE2C-BAC0-4D79-8482-CB9E7F328070}"/>
+    <hyperlink ref="A11" r:id="rId3" display="Blade Sicherung 30A" xr:uid="{6D31BE2C-BAC0-4D79-8482-CB9E7F328070}"/>
     <hyperlink ref="A16" r:id="rId4" xr:uid="{E0EF3F67-2FF3-43F5-A14B-C16CF9894C41}"/>
     <hyperlink ref="A20" r:id="rId5" xr:uid="{FA9498DA-3F24-4A1D-AE9E-9A40404541C7}"/>
     <hyperlink ref="A21" r:id="rId6" xr:uid="{FFE12644-12E8-4C78-8A30-54CE5B3B75AA}"/>
@@ -1070,26 +994,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1A147C5C4574A4CBD22C218932CFCEC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73e3fc346e235f1563653d0b735adab0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="934afb93-0c6a-4215-9c5f-1e6c0d084b74" xmlns:ns3="9772f75b-76b5-4c2b-8293-c04a292a8f98" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4bbf41fdf3feaa1d3e474fb90ecb8332" ns2:_="" ns3:_="">
     <xsd:import namespace="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
@@ -1296,26 +1200,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
-    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9772f75b-76b5-4c2b-8293-c04a292a8f98" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="934afb93-0c6a-4215-9c5f-1e6c0d084b74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE955B8-3D42-4FAD-A4B0-6AF905D6A50D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1332,4 +1237,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2AC9AE-123B-4552-9319-0D1FB7737CD7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBCB7549-A3C0-481E-86CB-91BDA585C95C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9772f75b-76b5-4c2b-8293-c04a292a8f98"/>
+    <ds:schemaRef ds:uri="934afb93-0c6a-4215-9c5f-1e6c0d084b74"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>